--- a/output/2026-09-02_13_Italia_Abruzzo_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-02_13_Italia_Abruzzo_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Commercio macchine utensili per lavorazione metalli; unita' locale confermata a Colonnella (TE), sede legale principale a San Benedetto del Tronto (Marche/AP); email non verificata in questa ricerca</t>
+          <t>Commercio macchine utensili per lavorazione metalli; unita' locale confermata a Colonnella (TE), sede legale principale a San Benedetto del Tronto (Marche/AP); email non verificata in questa ricerca [DUPLICATO — vedi anche: 2026-09-02_08_Italia_Abruzzo_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
